--- a/business_forms/039_time_tracking_summary_report_form--business_forms.xlsx
+++ b/business_forms/039_time_tracking_summary_report_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>business_form</t>
+          <t>business_form_page</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>business_form</t>
+          <t>What is the business form?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>start_time</t>
+          <t>start_time_page</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>start_time</t>
+          <t>Start Time</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>end_time</t>
+          <t>end_time_page</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>end_time</t>
+          <t>End Time</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>break_time</t>
+          <t>break_time_page</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>break_time</t>
+          <t>Break Time</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>work_log</t>
+          <t>work_log_page</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>work_log</t>
+          <t>Work Log</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>notes_page</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>Additional Notes</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>form_category_page</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>Form Category</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>form_sub_category</t>
+          <t>form_sub_category_page</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>form_sub_category</t>
+          <t>Form Sub Category</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,177 +704,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>assigned_tool_page</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>Assigned Tool</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>business_form</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>business_form</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>enterprise_form</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>enterprise_form</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>time_tracking_summary_report_form_business_forms</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>time_tracking_summary_report_form_business_forms</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>form_category</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>form_category</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>form_sub_category</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>form_sub_category</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -891,10 +730,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
@@ -919,7 +758,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>business_form_choices</t>
+          <t>business_form_page_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -936,7 +775,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>business_form_choices</t>
+          <t>business_form_page_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -953,7 +792,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>form_category_page_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -970,7 +809,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>form_category_choices</t>
+          <t>form_category_page_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -987,7 +826,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>form_sub_category_choices</t>
+          <t>form_sub_category_page_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1004,7 +843,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>form_sub_category_choices</t>
+          <t>form_sub_category_page_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1021,7 +860,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_page_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1038,7 +877,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_page_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1047,176 +886,6 @@
         </is>
       </c>
       <c r="C9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>time_tracking_summary_report_form_business_forms_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>time_tracking_summary_report_form_business_forms_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>assigned_tool_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>assigned_tool_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>form_category_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>business_forms</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Business Forms</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>form_category_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>personal_forms</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Personal Forms</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>form_sub_category_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>form_sub_category_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>assigned_tool_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>assigned_tool_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
         <is>
           <t>No</t>
         </is>
